--- a/data/trans_camb/P0901-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P0901-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 3,56</t>
+          <t>-1,4; 3,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,28</t>
+          <t>-3,03; 1,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 2,94</t>
+          <t>-3,35; 3,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 2,51</t>
+          <t>-3,46; 2,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 0,6</t>
+          <t>-4,34; 0,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 3,22</t>
+          <t>-4,62; 3,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 2,23</t>
+          <t>-1,6; 2,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 0,25</t>
+          <t>-3,29; 0,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 1,57</t>
+          <t>-3,29; 1,44</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,06; 174,16</t>
+          <t>-35,59; 192,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-75,95; 64,14</t>
+          <t>-74,65; 64,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-87,88; 195,75</t>
+          <t>-86,79; 181,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-51,66; 65,38</t>
+          <t>-52,15; 68,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-66,09; 23,67</t>
+          <t>-66,95; 27,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-76,49; 80,35</t>
+          <t>-75,31; 79,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-32,16; 69,88</t>
+          <t>-34,03; 62,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-61,11; 14,68</t>
+          <t>-68,21; 2,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-68,74; 50,64</t>
+          <t>-68,81; 43,38</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 2,39</t>
+          <t>-1,48; 2,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 3,55</t>
+          <t>-0,64; 3,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 8,08</t>
+          <t>1,25; 8,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,28; -0,48</t>
+          <t>-6,28; -0,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 0,84</t>
+          <t>-5,25; 0,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,89; -0,07</t>
+          <t>-6,99; -0,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 0,52</t>
+          <t>-2,95; 0,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 1,75</t>
+          <t>-1,94; 1,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 2,78</t>
+          <t>-1,75; 3,05</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-38,69; 113,32</t>
+          <t>-38,42; 111,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,95; 156,21</t>
+          <t>-17,74; 160,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,49; 333,46</t>
+          <t>29,24; 355,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-61,45; -5,07</t>
+          <t>-63,4; -3,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,16; 13,9</t>
+          <t>-52,88; 13,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,17; -1,16</t>
+          <t>-70,0; -4,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,63; 11,7</t>
+          <t>-46,86; 11,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,61; 39,57</t>
+          <t>-31,03; 39,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-27,74; 59,9</t>
+          <t>-28,8; 62,63</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 3,99</t>
+          <t>-0,95; 4,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 1,67</t>
+          <t>-2,81; 1,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 6,42</t>
+          <t>0,3; 6,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 6,09</t>
+          <t>-0,51; 6,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 2,76</t>
+          <t>-3,31; 3,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 4,84</t>
+          <t>-1,7; 4,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 4,61</t>
+          <t>-0,24; 4,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 1,55</t>
+          <t>-2,56; 1,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 4,79</t>
+          <t>-0,08; 4,5</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-18,21; 114,66</t>
+          <t>-17,04; 113,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-48,23; 47,59</t>
+          <t>-46,86; 49,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,07; 166,19</t>
+          <t>-0,09; 156,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 83,99</t>
+          <t>-4,91; 82,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,93; 37,13</t>
+          <t>-31,59; 38,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-14,54; 62,89</t>
+          <t>-15,71; 58,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 77,5</t>
+          <t>-3,6; 68,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,07; 26,2</t>
+          <t>-32,16; 22,87</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,38; 76,09</t>
+          <t>-1,94; 73,53</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 4,85</t>
+          <t>-1,66; 5,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 6,47</t>
+          <t>-0,54; 6,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 7,78</t>
+          <t>-4,03; 7,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 5,73</t>
+          <t>-3,05; 5,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 3,25</t>
+          <t>-5,1; 3,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 5,71</t>
+          <t>-2,42; 5,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 4,2</t>
+          <t>-1,12; 4,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 3,83</t>
+          <t>-1,35; 3,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 5,05</t>
+          <t>-3,39; 5,22</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 84,81</t>
+          <t>-19,44; 93,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 113,16</t>
+          <t>-7,48; 114,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-42,5; 121,54</t>
+          <t>-47,84; 125,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-16,52; 47,52</t>
+          <t>-18,2; 47,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,11; 27,18</t>
+          <t>-31,08; 27,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 49,03</t>
+          <t>-14,97; 47,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 44,77</t>
+          <t>-9,7; 48,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-12,36; 41,37</t>
+          <t>-11,35; 43,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-31,07; 50,32</t>
+          <t>-26,71; 53,87</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 5,48</t>
+          <t>-4,9; 5,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 2,46</t>
+          <t>-7,6; 2,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 9,38</t>
+          <t>-0,09; 9,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,78; 17,0</t>
+          <t>5,32; 17,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,46; 12,19</t>
+          <t>0,46; 11,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,75; 11,21</t>
+          <t>1,81; 11,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,09; 10,1</t>
+          <t>1,82; 9,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 5,74</t>
+          <t>-1,71; 5,72</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,22; 8,74</t>
+          <t>2,09; 9,2</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-24,88; 41,33</t>
+          <t>-26,83; 40,65</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-40,13; 19,35</t>
+          <t>-41,37; 18,35</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 70,63</t>
+          <t>-0,17; 71,87</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21,99; 111,15</t>
+          <t>25,27; 115,03</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,07; 83,02</t>
+          <t>1,5; 74,29</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,36; 78,64</t>
+          <t>7,47; 76,54</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,12; 67,01</t>
+          <t>10,03; 63,75</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 38,75</t>
+          <t>-9,57; 39,34</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>11,26; 58,16</t>
+          <t>10,49; 61,72</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1,46; 15,69</t>
+          <t>1,22; 15,48</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 6,9</t>
+          <t>-4,9; 6,86</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 4,08</t>
+          <t>-5,9; 4,98</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 13,04</t>
+          <t>-1,39; 12,75</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 11,79</t>
+          <t>-3,04; 11,28</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-29,37; -1,97</t>
+          <t>-26,2; -2,26</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,65; 11,45</t>
+          <t>1,74; 11,56</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 6,98</t>
+          <t>-2,14; 7,51</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-18,08; -1,49</t>
+          <t>-18,01; -1,24</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5,65; 102,34</t>
+          <t>6,4; 97,94</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-26,9; 44,53</t>
+          <t>-24,19; 45,03</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-29,66; 27,57</t>
+          <t>-26,48; 32,72</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 43,45</t>
+          <t>-3,92; 42,4</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 40,09</t>
+          <t>-8,12; 37,79</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-77,58; -5,98</t>
+          <t>-74,82; -6,96</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,9; 46,66</t>
+          <t>6,3; 47,72</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 28,41</t>
+          <t>-7,81; 30,51</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-62,33; -5,78</t>
+          <t>-63,13; -5,28</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,92; 21,26</t>
+          <t>2,72; 21,33</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 10,48</t>
+          <t>-6,55; 11,12</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 6,76</t>
+          <t>-8,55; 7,72</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8,87; 24,26</t>
+          <t>8,89; 24,07</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,63; 20,13</t>
+          <t>4,81; 20,83</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,13; 17,16</t>
+          <t>3,77; 17,13</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,6; 20,62</t>
+          <t>9,05; 20,57</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,42; 14,08</t>
+          <t>2,59; 14,39</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,58; 10,72</t>
+          <t>1,03; 11,06</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>6,95; 66,3</t>
+          <t>7,11; 68,89</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-17,35; 34,07</t>
+          <t>-16,2; 36,46</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-22,07; 21,05</t>
+          <t>-20,44; 24,97</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>17,51; 61,25</t>
+          <t>18,18; 58,28</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>7,14; 50,86</t>
+          <t>9,63; 51,24</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,33; 42,78</t>
+          <t>7,58; 42,49</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,44; 56,13</t>
+          <t>19,89; 53,8</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>5,25; 37,0</t>
+          <t>5,66; 37,33</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1,56; 28,06</t>
+          <t>2,23; 28,83</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,52</t>
+          <t>1,47; 4,54</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 2,86</t>
+          <t>0,07; 2,92</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,79</t>
+          <t>0,73; 5,68</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,41</t>
+          <t>2,56; 6,58</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,05</t>
+          <t>1,35; 4,99</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 4,78</t>
+          <t>-0,78; 4,92</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,92</t>
+          <t>2,54; 5,06</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,48</t>
+          <t>1,17; 3,6</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,74</t>
+          <t>1,03; 4,95</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>14,92; 53,7</t>
+          <t>14,95; 54,47</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 33,58</t>
+          <t>0,64; 35,0</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>12,55; 67,29</t>
+          <t>8,15; 66,62</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15,62; 41,1</t>
+          <t>14,64; 42,34</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>8,47; 32,48</t>
+          <t>7,75; 32,4</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 30,37</t>
+          <t>-3,93; 31,54</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,96; 40,72</t>
+          <t>19,02; 41,64</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>7,88; 28,49</t>
+          <t>8,63; 29,42</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>9,7; 39,08</t>
+          <t>8,1; 40,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P0901-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P0901-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,02</t>
+          <t>-1,23</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,28</t>
+          <t>-0,3</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,23</t>
+          <t>-0,82</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 3,68</t>
+          <t>-1,14; 3,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 1,2</t>
+          <t>-3,02; 1,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 3,14</t>
+          <t>-3,41; 2,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 2,36</t>
+          <t>-3,39; 2,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 0,73</t>
+          <t>-4,79; 0,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 3,01</t>
+          <t>-3,93; 4,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,07</t>
+          <t>-1,6; 2,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 0,11</t>
+          <t>-3,19; 0,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 1,44</t>
+          <t>-2,94; 1,86</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-32,73%</t>
+          <t>-39,44%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-24,68%</t>
+          <t>-5,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-29,87%</t>
+          <t>-19,95%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,59; 192,39</t>
+          <t>-28,98; 181,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-74,65; 64,34</t>
+          <t>-74,72; 60,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-86,79; 181,01</t>
+          <t>-89,68; 108,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-52,15; 68,47</t>
+          <t>-51,04; 68,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-66,95; 27,08</t>
+          <t>-69,29; 26,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-75,31; 79,8</t>
+          <t>-63,07; 115,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,03; 62,25</t>
+          <t>-33,2; 73,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-68,21; 2,44</t>
+          <t>-62,31; 13,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-68,81; 43,38</t>
+          <t>-63,86; 56,24</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,14</t>
+          <t>3,77</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,52</t>
+          <t>-2,99</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,58</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 2,31</t>
+          <t>-1,31; 2,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 3,63</t>
+          <t>-0,68; 3,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 8,44</t>
+          <t>0,69; 7,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,28; -0,31</t>
+          <t>-6,46; -0,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 0,9</t>
+          <t>-5,03; 0,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,99; -0,3</t>
+          <t>-5,83; 0,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 0,5</t>
+          <t>-3,05; 0,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 1,82</t>
+          <t>-1,92; 1,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 3,05</t>
+          <t>-1,55; 2,71</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>135,34%</t>
+          <t>123,44%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-42,79%</t>
+          <t>-36,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-38,42; 111,07</t>
+          <t>-34,36; 113,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,74; 160,84</t>
+          <t>-23,08; 168,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,24; 355,3</t>
+          <t>13,86; 321,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-63,4; -3,02</t>
+          <t>-64,84; -4,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,88; 13,55</t>
+          <t>-52,22; 13,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,0; -4,06</t>
+          <t>-60,94; 3,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,86; 11,16</t>
+          <t>-47,89; 9,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,03; 39,01</t>
+          <t>-31,48; 40,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-28,8; 62,63</t>
+          <t>-25,76; 56,18</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,32</t>
+          <t>2,47</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,47</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,32</t>
+          <t>1,8</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 4,11</t>
+          <t>-0,89; 4,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 1,67</t>
+          <t>-2,74; 1,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 6,43</t>
+          <t>-0,33; 5,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 6,22</t>
+          <t>-0,83; 5,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 3,01</t>
+          <t>-3,46; 3,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 4,4</t>
+          <t>-1,69; 4,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 4,22</t>
+          <t>-0,13; 4,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,39</t>
+          <t>-2,46; 1,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 4,5</t>
+          <t>-0,45; 3,86</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>25,4%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,04; 113,79</t>
+          <t>-18,19; 109,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-46,86; 49,84</t>
+          <t>-44,99; 52,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 156,97</t>
+          <t>-6,58; 147,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 82,93</t>
+          <t>-7,24; 74,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-31,59; 38,72</t>
+          <t>-30,94; 40,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 58,64</t>
+          <t>-16,32; 57,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 68,22</t>
+          <t>-1,17; 67,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-32,16; 22,87</t>
+          <t>-30,75; 24,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 73,53</t>
+          <t>-7,11; 61,23</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>6,4</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,64</t>
+          <t>2,04</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>4,26</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 5,1</t>
+          <t>-2,06; 4,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 6,5</t>
+          <t>-0,16; 6,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 7,7</t>
+          <t>3,11; 10,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 5,69</t>
+          <t>-2,79; 5,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 3,31</t>
+          <t>-4,77; 2,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 5,6</t>
+          <t>-1,92; 5,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 4,45</t>
+          <t>-1,14; 4,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 3,99</t>
+          <t>-1,66; 3,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 5,22</t>
+          <t>1,6; 6,73</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>39,89%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-19,44; 93,87</t>
+          <t>-21,87; 90,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 114,37</t>
+          <t>-3,34; 124,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-47,84; 125,94</t>
+          <t>34,77; 185,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-18,2; 47,65</t>
+          <t>-17,6; 44,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,08; 27,08</t>
+          <t>-29,2; 23,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 47,15</t>
+          <t>-11,25; 48,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 48,07</t>
+          <t>-9,34; 43,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 43,07</t>
+          <t>-13,76; 41,75</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-26,71; 53,87</t>
+          <t>11,74; 72,85</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4,77</t>
+          <t>4,13</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,47</t>
+          <t>6,98</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,57</t>
+          <t>5,53</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 5,22</t>
+          <t>-4,67; 5,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 2,42</t>
+          <t>-7,97; 2,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 9,23</t>
+          <t>-1,19; 8,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,32; 17,05</t>
+          <t>5,32; 16,72</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,46; 11,38</t>
+          <t>0,8; 12,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,81; 11,29</t>
+          <t>2,06; 11,78</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,82; 9,75</t>
+          <t>1,8; 9,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 5,72</t>
+          <t>-1,89; 5,46</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,09; 9,2</t>
+          <t>2,09; 8,91</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-26,83; 40,65</t>
+          <t>-24,74; 42,81</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-41,37; 18,35</t>
+          <t>-42,93; 18,48</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 71,87</t>
+          <t>-7,64; 66,84</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25,27; 115,03</t>
+          <t>25,69; 106,86</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,5; 74,29</t>
+          <t>4,11; 83,68</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,47; 76,54</t>
+          <t>9,52; 80,54</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,03; 63,75</t>
+          <t>9,7; 63,03</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 39,34</t>
+          <t>-9,92; 36,66</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>10,49; 61,72</t>
+          <t>10,35; 61,04</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-0,62</t>
+          <t>-1,08</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-14,09</t>
+          <t>-3,87</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-7,73</t>
+          <t>-2,84</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1,22; 15,48</t>
+          <t>0,78; 14,64</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 6,86</t>
+          <t>-5,33; 6,87</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 4,98</t>
+          <t>-6,81; 4,05</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 12,75</t>
+          <t>-1,19; 12,56</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 11,28</t>
+          <t>-3,99; 11,12</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-26,2; -2,26</t>
+          <t>-9,79; 1,66</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,74; 11,56</t>
+          <t>1,98; 11,38</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 7,51</t>
+          <t>-2,22; 7,26</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-18,01; -1,24</t>
+          <t>-7,05; 1,37</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-3,36%</t>
+          <t>-5,87%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-41,77%</t>
+          <t>-11,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-28,99%</t>
+          <t>-10,66%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6,4; 97,94</t>
+          <t>3,46; 91,95</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-24,19; 45,03</t>
+          <t>-25,59; 43,93</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 32,72</t>
+          <t>-30,08; 28,66</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 42,4</t>
+          <t>-3,27; 41,73</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 37,79</t>
+          <t>-10,3; 36,15</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-74,82; -6,96</t>
+          <t>-25,82; 5,44</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,3; 47,72</t>
+          <t>6,6; 45,99</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 30,51</t>
+          <t>-7,96; 29,14</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-63,13; -5,28</t>
+          <t>-23,67; 5,68</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-1,01</t>
+          <t>-0,85</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,47</t>
+          <t>11,1</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,77</t>
+          <t>6,19</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,72; 21,33</t>
+          <t>3,06; 21,49</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 11,12</t>
+          <t>-7,3; 9,96</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 7,72</t>
+          <t>-8,84; 6,91</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8,89; 24,07</t>
+          <t>8,55; 24,73</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,81; 20,83</t>
+          <t>4,62; 19,86</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,77; 17,13</t>
+          <t>4,33; 18,06</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,05; 20,57</t>
+          <t>9,0; 20,79</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,59; 14,39</t>
+          <t>2,8; 14,82</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,03; 11,06</t>
+          <t>1,33; 11,14</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-2,79%</t>
+          <t>-2,34%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>7,11; 68,89</t>
+          <t>6,81; 67,93</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 36,46</t>
+          <t>-17,39; 31,77</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-20,44; 24,97</t>
+          <t>-21,06; 22,31</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18,18; 58,28</t>
+          <t>16,87; 61,81</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>9,63; 51,24</t>
+          <t>9,73; 50,17</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,58; 42,49</t>
+          <t>8,23; 44,53</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,89; 53,8</t>
+          <t>19,94; 53,39</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>5,66; 37,33</t>
+          <t>6,29; 38,9</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2,23; 28,83</t>
+          <t>2,7; 29,15</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3,93</t>
+          <t>4,58</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>4,39</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3,36</t>
+          <t>4,53</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,54</t>
+          <t>1,37; 4,47</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,07; 2,92</t>
+          <t>-0,08; 2,96</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,73; 5,68</t>
+          <t>3,03; 6,17</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,56; 6,58</t>
+          <t>2,51; 6,55</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,99</t>
+          <t>1,22; 5,02</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 4,92</t>
+          <t>2,65; 6,0</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,06</t>
+          <t>2,44; 4,94</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,6</t>
+          <t>1,16; 3,5</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,95</t>
+          <t>3,41; 5,75</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>14,95; 54,47</t>
+          <t>14,52; 54,36</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>0,64; 35,0</t>
+          <t>-0,97; 35,69</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8,15; 66,62</t>
+          <t>31,09; 73,95</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14,64; 42,34</t>
+          <t>14,46; 42,39</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>7,75; 32,4</t>
+          <t>6,97; 32,85</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 31,54</t>
+          <t>15,5; 39,32</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,02; 41,64</t>
+          <t>18,39; 40,55</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>8,63; 29,42</t>
+          <t>8,71; 28,63</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>8,1; 40,04</t>
+          <t>25,65; 47,89</t>
         </is>
       </c>
     </row>
